--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -7,10 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="横浜FM-鹿島_807" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="川崎-京都サンガＦ．Ｃ．_815" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="名古屋-清水_808" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="東京V-柏_814" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="横浜FM_808" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FC東京_823" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="水戸_807" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="浦和_815" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="千葉_808" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="川崎F_815" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="柏_808" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="町田_829" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="鹿島_814" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="東京V_821" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,199 +433,417 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>バックアッパー(ホーム)３層</t>
+          <t>アウェイゴール裏自由</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>バックＳＢ １層(ホーム)</t>
+          <t>アビスパシート指定</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>バックＳＢ ２層(ホーム)</t>
+          <t>ウェルカムシート自由</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>バックＳＣ １層(ホーム)</t>
+          <t>エキサイティングシート指定</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>バックＳＣ １層(ミックス)</t>
+          <t>バックスタンド自由（Ｂ１）</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バックＳＣ ２層(ホーム)</t>
+          <t>バックスタンド自由（Ｂ７）</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>バックＳＣ ２層(ミックス)</t>
+          <t>ピッチサイドシート指定（Ｂ２）</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ビジターサポーターズシート１層</t>
+          <t>ピッチサイドシート指定（Ｂ６）</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ビジターサポーターズシート２層</t>
+          <t>プレミアムシート指定</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ホームサポーターズシート１層</t>
+          <t>ホームゴール裏自由</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ホームサポーターズシート２層</t>
+          <t>メインスタンド指定（Ｍ１）</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ホームパノラマシート３層</t>
+          <t>メインスタンド指定（Ｍ２）</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ミックスパノラマシート３層</t>
+          <t>メインスタンド指定（Ｍ５）</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>メインＳＡ ３層(ホーム)</t>
+          <t>メインスタンド指定（Ｍ６）</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>メインＳＡ ３層(ミックス)</t>
+          <t>メインスタンド自由（Ｍ１）</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>メインＳＳ １層(ホーム)</t>
+          <t>メインスタンド自由（Ｍ６）</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>メインＳＳ １層(ミックス)</t>
+          <t>柴田産業Axion指定</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>メインＳＳ ２層(ホーム)</t>
+          <t>車いす席　平面駐車場付</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>メインＳＳ ２層(ミックス)</t>
+          <t>車いす席　立体駐車場付</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26 10:09</t>
+          <t>2026-07-26 10:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>クッション付きシート　北側</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>クッション付きシート　南側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>セブン-イレブンシート</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>バック</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バックセンター</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バックセンターＵＦ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バックＵＦ</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ビジター</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ホーム</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ホームＵＦ</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>メイン上層</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>メインＳ　北側</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>メインＳ　南側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>メインＳＳ　北側</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>メインＳＳ　南側</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>メインＳＳＳ</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ユニバーサル席　代表者</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ユニバーサル席　同伴者</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>南サイド</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>5,400</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6,200 完売</t>
+          <t>5,400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>5,400</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>6,000 完売</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>4,100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4,800 完売</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4,600 完売</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>6,300</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4,400</t>
+          <t>6,300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>8,700</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5,800</t>
+          <t>8,700</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>7,400</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>8,200 完売</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>8,200 完売</t>
+          <t>3,900</t>
         </is>
       </c>
     </row>
@@ -634,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,299 +869,209 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ごちクルグループシート６</t>
+          <t>カテゴリー１北（１層）</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>グループシート４</t>
+          <t>カテゴリー１南（１層）</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>セブンイレブンピッチサイド席</t>
+          <t>カテゴリー２北（１層）</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>テーブル付ペアシート</t>
+          <t>カテゴリー２南（１層）</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>バック車椅子席</t>
+          <t>カテゴリー３（１層）</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バックＳ指定北側</t>
+          <t>カテゴリー３（２層）</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>バックＳ指定南側</t>
+          <t>カテゴリー４北（１層）</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>バックＳＳ指定</t>
+          <t>カテゴリー４北（２層）</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ビジターＡ自由</t>
+          <t>カテゴリー４南（１層）</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ビジターＳ指定</t>
+          <t>カテゴリー４南（２層）</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ビジターＳＡ指定</t>
+          <t>カテゴリー５</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ファミリーシート３</t>
+          <t>ゼルビアサポーターズシート立見席</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ファミリーシート４</t>
+          <t>バック上層（３層）自由席</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>ファミリーシート６</t>
+          <t>ビジターサポーターズシート指定席</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ペアシート北側</t>
+          <t>プレミアムシート(ラウンジ付)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ペアシート南側</t>
+          <t>プレミアムシート（２層）</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ホームＡ指定</t>
+          <t>メイン上層（２層）</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ホームＡ自由</t>
+          <t>メイン上層（３層）</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>メイン車椅子席</t>
+          <t>南サイド（２・３層）</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>メインＳ指定北側</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>メインＳ指定南側</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>メインＳＳ指定上層中央</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>メインＳＳ指定下層北側</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>メインＳＳ指定下層南側</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ＳＡ指定北側</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ＳＡ指定南側</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ＳＧ指定</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ＳＳＳ指定</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>ＴＨＥＲＭＯＳ パーティーシート</t>
+          <t>車椅子同行者席</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26 10:09</t>
+          <t>2026-07-26 10:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7,200 完売</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6,000 完売</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6,000 完売</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>7,400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6,400 完売</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5,800</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7,000 完売</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3,700 完売</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6,400 完売</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4,700 完売</t>
+          <t>3,300</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>6,000 完売</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6,000 完売</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>6,000 完売</t>
+          <t>4,100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>7,100 完売</t>
+          <t>23,500</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>6,700 完売</t>
+          <t>12,100</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>6,600 完売</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>6,100</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>7,400 完売</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7,800 完売</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>7,400 完売</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4,600 完売</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>5,300 完売</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8,700 完売</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>7,700 完売</t>
+          <t>7,700</t>
         </is>
       </c>
     </row>
@@ -952,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,77 +1097,97 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>アウェイ指定席</t>
+          <t>バックアッパー(ホーム)３層</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席１階北側</t>
+          <t>バックＳＢ １層(ホーム)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席１階南側</t>
+          <t>バックＳＢ ２層(ホーム)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席２階北側</t>
+          <t>バックＳＣ １層(ホーム)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>セブン-イレブン最前列シート</t>
+          <t>バックＳＣ １層(ミックス)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バック３階指定席</t>
+          <t>バックＳＣ ２層(ホーム)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>バック４階指定席</t>
+          <t>バックＳＣ ２層(ミックス)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>メイン３階指定席</t>
+          <t>ビジターサポーターズシート１層</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>メイン４階指定席</t>
+          <t>ビジターサポーターズシート２層</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ロイヤルシート</t>
+          <t>ホームサポーターズシート１層</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Ａ指定席</t>
+          <t>ホームサポーターズシート２層</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Ｂ指定席</t>
+          <t>ホームパノラマシート３層</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Ｃ指定席</t>
+          <t>ミックスパノラマシート３層</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Ｓ指定席</t>
+          <t>メインＳＡ ３層(ホーム)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ＳＳ指定席</t>
+          <t>メインＳＡ ３層(ミックス)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>メインＳＳ １層(ホーム)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>メインＳＳ １層(ミックス)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>メインＳＳ ２層(ホーム)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>メインＳＳ ２層(ミックス)</t>
         </is>
       </c>
     </row>
@@ -1045,77 +1199,199 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>5,000 完売</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9,200</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>4,800</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5,200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>12,000 完売</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>7,200</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>7,200</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>8,200</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>9,600</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,87 +1417,147 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ゴール裏ビジター指定</t>
+          <t>ごちクルグループシート６</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ゴール裏ホーム自由</t>
+          <t>グループシート４</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ゴール裏ホーム自由3層</t>
+          <t>セブンイレブンピッチサイド席</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>サイドミックス指定3層</t>
+          <t>テーブル付ペアシート</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>バックホーム指定</t>
+          <t>バック車椅子席</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バックホーム指定3層</t>
+          <t>バックＳ指定北側</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>バックホーム指定センター</t>
+          <t>バックＳ指定南側</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>バックミックス指定</t>
+          <t>バックＳＳ指定</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>バックミックス指定3層</t>
+          <t>ビジターＡ自由</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>プレミアムシートホームラウンジ付</t>
+          <t>ビジターＳ指定</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>プレミアムシートミックスラウンジ付</t>
+          <t>ビジターＳＡ指定</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>メインSS指定ホーム</t>
+          <t>ファミリーシート３</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>メインSS指定ミックス</t>
+          <t>ファミリーシート４</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>メインS指定ホーム</t>
+          <t>ファミリーシート６</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>メインS指定ミックス</t>
+          <t>ペアシート北側</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>メイン指定ホーム3層</t>
+          <t>ペアシート南側</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>メイン指定ミックス3層</t>
+          <t>ホームＡ指定</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームＡ自由</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>メイン車椅子席</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>メインＳ指定北側</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>メインＳ指定南側</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定上層中央</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定下層北側</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定下層南側</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定北側</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定南側</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ＳＧ指定</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ＳＳＳ指定</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ＴＨＥＲＭＯＳ パーティーシート</t>
         </is>
       </c>
     </row>
@@ -1233,6 +1569,1260 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>アウェイ指定席</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ゴール裏指定席１階北側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ゴール裏指定席１階南側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ゴール裏指定席２階北側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>セブン-イレブン最前列シート</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バック３階指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バック４階指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メイン３階指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>メイン４階指定席</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ロイヤルシート</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Ａ指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Ｂ指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Ｃ指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ＳＳ指定席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>バック指定席（ホーム）</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ビジター指定席</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホーム応援エリア席</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインミックス指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席　北</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席　南</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ＳＢ指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ＳＳ指定席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>カテゴリー４</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>カテゴリー４ミックス</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>カテゴリー４ミックス視界制限席</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>カテゴリー４視界制限席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>カテゴリー５</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>カテゴリー５視界制限席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>カテゴリー６指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>カテゴリー６自由席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ガンバサポーターシート</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ビジター指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>モリタにこにこ家族ラウンジ</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>車椅子ミックス席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>車椅子席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ゴール裏ビジター指定</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ゴール裏ホーム自由</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ゴール裏ホーム自由3層</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>サイドミックス指定3層</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バックホーム指定</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バックホーム指定3層</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バックホーム指定センター</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>バックミックス指定</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>バックミックス指定3層</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>プレミアムシートホームラウンジ付</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>プレミアムシートミックスラウンジ付</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>メインSS指定ホーム</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>メインSS指定ミックス</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>メインS指定ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>メインS指定ミックス</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>メイン指定ホーム3層</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>メイン指定ミックス3層</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>4,500 [変動]</t>
         </is>
       </c>
@@ -1312,6 +2902,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>5,600 [変動]</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="横浜FM_808" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FC東京_823" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="水戸_807" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="浦和_815" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="千葉_808" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="川崎F_815" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="柏_808" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="町田_829" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="鹿島_814" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="東京V_821" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="福岡-横浜FM_808" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="町田-FC東京_823" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="横浜FM-水戸_807" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="川崎-浦和_815" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="名古屋-千葉_808" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="岡山-川崎F_815" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="C大阪-柏_808" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="G大阪-町田_829" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="東京V-鹿島_814" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FC東京-東京V_821" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -640,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,6 +944,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>3,900</t>
         </is>
@@ -858,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1274,113 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1086,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,6 +1701,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>8,200 完売</t>
         </is>
@@ -1406,7 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1860,6 +2273,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>7,700 完売</t>
         </is>
@@ -1876,7 +2441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2120,6 +2685,88 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>9,600</t>
         </is>
@@ -2136,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2238,6 +2885,58 @@
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -2254,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2546,6 +3245,153 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -2562,7 +3408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2704,6 +3550,78 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>5,600</t>
         </is>
@@ -2720,7 +3638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2994,6 +3912,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>5,600 [変動]</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -12,11 +12,12 @@
     <sheet name="横浜FM-鹿島_807" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="川崎F-京都_815" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="名古屋-清水_808" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="岡山-長崎_815" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="C大阪-岡山_808" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="G大阪-広島_829" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="東京V-柏_814" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="FC東京-千葉_821" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="京都-水戸_822" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="岡山-長崎_815" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="C大阪-岡山_808" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="G大阪-広島_829" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="東京V-柏_814" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FC東京-千葉_821" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +625,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -640,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,97 +754,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>クッション付きシート　北側</t>
+          <t>ゴール裏ビジター指定</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>クッション付きシート　南側</t>
+          <t>ゴール裏ホーム自由</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>セブン-イレブンシート</t>
+          <t>ゴール裏ホーム自由3層</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>バック</t>
+          <t>サイドミックス指定3層</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>バックセンター</t>
+          <t>バックホーム指定</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バックセンターＵＦ</t>
+          <t>バックホーム指定3層</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>バックＵＦ</t>
+          <t>バックホーム指定センター</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ビジター</t>
+          <t>バックミックス指定</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ホーム</t>
+          <t>バックミックス指定3層</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ホームＵＦ</t>
+          <t>プレミアムシートホームラウンジ付</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>メイン上層</t>
+          <t>プレミアムシートミックスラウンジ付</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>メインＳ　北側</t>
+          <t>メインSS指定ホーム</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>メインＳ　南側</t>
+          <t>メインSS指定ミックス</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>メインＳＳ　北側</t>
+          <t>メインS指定ホーム</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>メインＳＳ　南側</t>
+          <t>メインS指定ミックス</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>メインＳＳＳ</t>
+          <t>メイン指定ホーム3層</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ユニバーサル席　代表者</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ユニバーサル席　同伴者</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>南サイド</t>
+          <t>メイン指定ミックス3層</t>
         </is>
       </c>
     </row>
@@ -753,6 +846,306 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>クッション付きシート　北側</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>クッション付きシート　南側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>セブン-イレブンシート</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>バック</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バックセンター</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バックセンターＵＦ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バックＵＦ</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ビジター</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ホーム</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ホームＵＦ</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>メイン上層</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>メインＳ　北側</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>メインＳ　南側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>メインＳＳ　北側</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>メインＳＳ　南側</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>メインＳＳＳ</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ユニバーサル席　代表者</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ユニバーサル席　同伴者</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>南サイド</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:49</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>11,500</t>
         </is>
       </c>
@@ -842,6 +1235,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>3,900</t>
         </is>
@@ -858,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1565,113 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1086,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,6 +1890,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>8,200 完売</t>
         </is>
@@ -1304,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,6 +2310,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>7,700 完売</t>
         </is>
@@ -1622,7 +2478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,6 +2640,88 @@
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>9,600</t>
         </is>
@@ -1800,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,99 +2749,219 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>バック指定席（ホーム）</t>
+          <t>エキサイティングシート</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>サンガシート</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サンガプレミアムシート</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>バックエキサイティングシート</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バック上層フロントシート</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バック上層Ａ指定席北側</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バック上層Ａ指定席南側</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>バック上層Ｓ指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>バックＡ指定席北側</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バックＡ指定席南側</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バックＳ指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>バルコニー上層指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>バルコニー指定席１・４</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バルコニー指定席２・３</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>ビジター指定席</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ホーム応援エリア席</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>メインミックス指定席</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Ｓ指定席　北</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Ｓ指定席　南</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ＳＡ指定席</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ＳＢ指定席</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ＳＳ指定席</t>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホーム上層指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホーム指定席（立見可能）</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>メインＳ指定席北側</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>メインＳ指定席南側</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>南サイドホーム上層自由席</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>南サイド指定席</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26 10:49</t>
+          <t>2026-07-26 10:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>9,000 完売</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>6,900 完売</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>12,500 完売</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5,200</t>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1,800 完売</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
         </is>
       </c>
     </row>
@@ -1918,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1929,142 +2987,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>エキサイティングシート(ホーム)前方</t>
+          <t>バック指定席（ホーム）</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>エキサイティングシート（ホーム）</t>
+          <t>ビジター指定席</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>バックセンターシート上段ホーム</t>
+          <t>ホーム応援エリア席</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>バックセンターシート下段ホーム</t>
+          <t>メインミックス指定席</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>バリュープライスシートAホーム</t>
+          <t>Ｓ指定席　北</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バリュープライスシートBホーム</t>
+          <t>Ｓ指定席　南</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ビジターサポーター指定席</t>
+          <t>ＳＡ指定席</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ホームサポーター指定席</t>
+          <t>ＳＢ指定席</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ホームサポーター自由席</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ホームバック北A指定席上段</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ホームバック北A指定席下段</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ホームバック北B指定席上段</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ホームバック北B指定席下段</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ホームバック南A指定席上段</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ホームバック南A指定席下段</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ホームバック南B指定席上段</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ホームバック南B指定席下段</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ホームメインセンターA指定席</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ホームメイン北A指定席</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>ホームメイン北SS指定席</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>ホームメイン北SS指定席前方</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ホームメイン北S指定席</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ホームメイン北S指定席前方</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>ホームメイン南A指定席</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ホームメイン南SS指定席</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ホームメイン南SS指定席前方</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ミックスメイン南S指定席</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ミックスメイン南S指定席前方</t>
+          <t>ＳＳ指定席</t>
         </is>
       </c>
     </row>
@@ -2076,142 +3039,99 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13,800 完売</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12,800 完売</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5,000 完売</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5,800 完売</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2,500 完売</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>4,800</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>5,400 完売</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5,000 完売</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3,300</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>7,300 完売</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>5,700 完売</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>8,600 完売</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>9,600 完売</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>7,200</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>8,200 完売</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>8,900</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>9,900 完売</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>7,000 完売</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8,000</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,200</t>
         </is>
       </c>
     </row>
@@ -2226,7 +3146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2237,67 +3157,142 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>カテゴリー４</t>
+          <t>エキサイティングシート(ホーム)前方</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>カテゴリー４ミックス</t>
+          <t>エキサイティングシート（ホーム）</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>カテゴリー４ミックス視界制限席</t>
+          <t>バックセンターシート上段ホーム</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>カテゴリー４視界制限席</t>
+          <t>バックセンターシート下段ホーム</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>カテゴリー５</t>
+          <t>バリュープライスシートAホーム</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>カテゴリー５視界制限席</t>
+          <t>バリュープライスシートBホーム</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>カテゴリー６指定席</t>
+          <t>ビジターサポーター指定席</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>カテゴリー６自由席</t>
+          <t>ホームサポーター指定席</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ガンバサポーターシート</t>
+          <t>ホームサポーター自由席</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ビジター指定席</t>
+          <t>ホームバック北A指定席上段</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>モリタにこにこ家族ラウンジ</t>
+          <t>ホームバック北A指定席下段</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>車椅子ミックス席</t>
+          <t>ホームバック北B指定席上段</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>車椅子席</t>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
         </is>
       </c>
     </row>
@@ -2309,67 +3304,289 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>13,800 完売</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>12,800 完売</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>7,500</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>5,600</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>5,600</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -2384,7 +3601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2395,87 +3612,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ゴール裏ビジター指定</t>
+          <t>カテゴリー４</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ゴール裏ホーム自由</t>
+          <t>カテゴリー４ミックス</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ゴール裏ホーム自由3層</t>
+          <t>カテゴリー４ミックス視界制限席</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>サイドミックス指定3層</t>
+          <t>カテゴリー４視界制限席</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>バックホーム指定</t>
+          <t>カテゴリー５</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>バックホーム指定3層</t>
+          <t>カテゴリー５視界制限席</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>バックホーム指定センター</t>
+          <t>カテゴリー６指定席</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>バックミックス指定</t>
+          <t>カテゴリー６自由席</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>バックミックス指定3層</t>
+          <t>ガンバサポーターシート</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>プレミアムシートホームラウンジ付</t>
+          <t>ビジター指定席</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>プレミアムシートミックスラウンジ付</t>
+          <t>モリタにこにこ家族ラウンジ</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>メインSS指定ホーム</t>
+          <t>車椅子ミックス席</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>メインSS指定ミックス</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>メインS指定ホーム</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>メインS指定ミックス</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>メイン指定ホーム3層</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>メイン指定ミックス3層</t>
+          <t>車椅子席</t>
         </is>
       </c>
     </row>
@@ -2487,87 +3684,139 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4,500 [変動]</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3,300</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4,100 [変動]</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6,100 [変動]</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5,200 [変動]</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14,600 [変動]</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>7,500</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>10,000 [変動]</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>6,500</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>8,800 [変動]</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>4,700</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>5,600 [変動]</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,600</t>
         </is>
       </c>
     </row>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
@@ -641,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,6 +955,113 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -869,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1220,78 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -1027,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,6 +1510,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -1245,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1790,88 @@
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -1423,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,6 +2180,153 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -1731,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,6 +2525,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -1929,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2231,6 +2935,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -2247,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2349,6 +3205,58 @@
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -2365,7 +3273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2567,6 +3475,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -2583,7 +3593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2805,6 +3815,118 @@
         </is>
       </c>
       <c r="V2" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26 16:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1,800 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
@@ -743,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1164,113 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1078,7 +1287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,6 +1501,78 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -1308,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1612,6 +1893,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -1628,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,6 +2255,88 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -1888,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2327,6 +2792,153 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -2343,7 +2955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2617,6 +3229,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -2633,7 +3337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3087,6 +3791,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -3103,7 +3959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,6 +4113,58 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -3273,7 +4181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3577,6 +4485,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -3593,7 +4603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3927,6 +4937,118 @@
         </is>
       </c>
       <c r="V3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1,800 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,6 +829,108 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
@@ -845,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1271,6 +1373,113 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1287,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1782,78 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -1589,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1995,6 +2276,108 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -2011,7 +2394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2337,6 +2720,88 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -2353,7 +2818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2939,6 +3404,153 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -2955,7 +3567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3321,6 +3933,98 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -3337,7 +4041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3943,6 +4647,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -3959,7 +4815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4165,6 +5021,58 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -4181,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4587,6 +5495,108 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -4603,7 +5613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5049,6 +6059,118 @@
         </is>
       </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1,800 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,6 +933,108 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
         </is>
       </c>
     </row>
@@ -947,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1582,113 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1496,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,6 +2063,78 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -1870,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2378,6 +2659,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -2394,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +3185,88 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -2818,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3551,6 +4016,153 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -3567,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4025,6 +4637,98 @@
         </is>
       </c>
       <c r="R5" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -4041,7 +4745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4799,6 +5503,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -4815,7 +5671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5073,6 +5929,58 @@
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -5089,7 +5997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5597,6 +6505,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -5613,7 +6623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6171,6 +7181,118 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,6 +1033,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
@@ -1049,7 +1151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1689,6 +1791,113 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1705,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2135,6 +2344,78 @@
         </is>
       </c>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:51</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -2151,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2761,6 +3042,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:51</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -2777,7 +3160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3650,88 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -3283,7 +3748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4163,6 +4628,153 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -4179,7 +4791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4729,6 +5341,98 @@
         </is>
       </c>
       <c r="R6" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -4745,7 +5449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5655,6 +6359,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -5671,7 +6527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5981,6 +6837,58 @@
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:51</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -5997,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6607,6 +7515,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -6623,7 +7633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7293,6 +8303,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:51</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,6 +1135,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
@@ -1151,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +2000,113 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -1914,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2625,78 @@
         </is>
       </c>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -2432,7 +2713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3144,6 +3425,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -3160,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,6 +4115,88 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -3748,7 +4213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4775,6 +5240,153 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -4791,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5433,6 +6045,98 @@
         </is>
       </c>
       <c r="R7" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -5449,7 +6153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6511,6 +7215,158 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -6527,7 +7383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6889,6 +7745,58 @@
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -6905,7 +7813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7617,6 +8525,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -7633,7 +8643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8415,6 +9425,118 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1237,6 +1237,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
@@ -1253,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2107,6 +2209,113 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22,800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -2123,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2906,78 @@
         </is>
       </c>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -2713,7 +2994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,6 +3808,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -3543,7 +3926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4197,6 +4580,88 @@
         </is>
       </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -4213,7 +4678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5387,6 +5852,153 @@
         </is>
       </c>
       <c r="AC8" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -5403,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6137,6 +6749,98 @@
         </is>
       </c>
       <c r="R8" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -6153,7 +6857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7367,6 +8071,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -7383,7 +8239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7797,6 +8653,58 @@
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -7813,7 +8721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8627,6 +9535,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -8643,7 +9653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9537,6 +10547,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,6 +1339,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
@@ -1355,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2316,6 +2418,113 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22,800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -2332,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2978,6 +3187,78 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -2994,7 +3275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3910,6 +4191,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -3926,7 +4309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +5045,88 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -4678,7 +5143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5999,6 +6464,153 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -6015,7 +6627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6841,6 +7453,98 @@
         </is>
       </c>
       <c r="R9" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -6857,7 +7561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8223,6 +8927,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -8239,7 +9095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8705,6 +9561,58 @@
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -8721,7 +9629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9637,6 +10545,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -9653,7 +10663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10659,6 +11669,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,6 +1441,108 @@
         </is>
       </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
@@ -1457,7 +1559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2525,6 +2627,113 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22,200</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -2541,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3259,6 +3468,78 @@
         </is>
       </c>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -3275,7 +3556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4293,6 +4574,108 @@
         </is>
       </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -4309,7 +4692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5127,6 +5510,88 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -5143,7 +5608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6611,6 +7076,153 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -6627,7 +7239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7545,6 +8157,98 @@
         </is>
       </c>
       <c r="R10" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5,600 [変動]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -7561,7 +8265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9079,6 +9783,158 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -9095,7 +9951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9613,6 +10469,58 @@
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -9629,7 +10537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10647,6 +11555,108 @@
         </is>
       </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -10663,7 +11673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11783,6 +12793,118 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
         </is>
       </c>
     </row>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,108 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
@@ -1559,7 +1661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,6 +2836,113 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -2750,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3540,6 +3749,78 @@
         </is>
       </c>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -3556,7 +3837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4676,6 +4957,108 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -4692,7 +5075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5592,6 +5975,88 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -5608,7 +6073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7223,6 +7688,153 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -7239,7 +7851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8249,6 +8861,98 @@
         </is>
       </c>
       <c r="R11" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5,700 [変動]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,300 [変動]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -8265,7 +8969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9935,6 +10639,158 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -9951,7 +10807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10521,6 +11377,58 @@
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -10537,7 +11445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11657,6 +12565,108 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -11673,7 +12683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12903,6 +13913,118 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>4,300 完売</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,6 +1647,108 @@
       <c r="T12" t="inlineStr">
         <is>
           <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,300</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2943,6 +3045,113 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -2959,7 +3168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3821,6 +4030,78 @@
         </is>
       </c>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -3837,7 +4118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5059,6 +5340,108 @@
         </is>
       </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -5075,7 +5458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6057,6 +6440,88 @@
         </is>
       </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -6073,7 +6538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7835,6 +8300,153 @@
         </is>
       </c>
       <c r="AC12" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -7851,7 +8463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8955,6 +9567,98 @@
       <c r="R12" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9,300 [変動]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,200 [変動]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,700 [変動]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5,800 [変動]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,800 [変動]</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
         </is>
       </c>
     </row>
@@ -8969,7 +9673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10791,6 +11495,158 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -10807,7 +11663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11429,6 +12285,58 @@
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -11445,7 +12353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12667,6 +13575,108 @@
         </is>
       </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -12683,7 +13693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14027,6 +15037,118 @@
       <c r="V12" t="inlineStr">
         <is>
           <t>4,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10,800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2,200 完売</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>4,300</t>
         </is>
       </c>
     </row>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1749,6 +1749,108 @@
       <c r="T13" t="inlineStr">
         <is>
           <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4,500</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3152,6 +3254,113 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -3168,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4102,6 +4311,78 @@
         </is>
       </c>
       <c r="N13" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -4118,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5442,6 +5723,108 @@
         </is>
       </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15,700 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -5458,7 +5841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6522,6 +6905,88 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -6538,7 +7003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8447,6 +8912,153 @@
         </is>
       </c>
       <c r="AC13" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -8463,7 +9075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9657,6 +10269,98 @@
         </is>
       </c>
       <c r="R13" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9,600 [変動]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,500 [変動]</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5,900 [変動]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5,800 [変動]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4,900 [変動]</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -9673,7 +10377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11647,6 +12351,158 @@
         </is>
       </c>
       <c r="AD13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -11663,7 +12519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12337,6 +13193,58 @@
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -12353,7 +13261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13677,6 +14585,108 @@
         </is>
       </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -13693,7 +14703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15147,6 +16157,118 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10,800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2,300 完売</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>4,300</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1851,6 +1851,108 @@
       <c r="T14" t="inlineStr">
         <is>
           <t>4,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,800</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3361,6 +3463,113 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -3377,7 +3586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4383,6 +4592,78 @@
         </is>
       </c>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -4399,7 +4680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5825,6 +6106,108 @@
         </is>
       </c>
       <c r="T14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15,700 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9,100 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -5841,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6987,6 +7370,88 @@
         </is>
       </c>
       <c r="P14" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -7003,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9059,6 +9524,153 @@
         </is>
       </c>
       <c r="AC14" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -9075,7 +9687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10361,6 +10973,98 @@
         </is>
       </c>
       <c r="R14" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9,900 [変動]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,100 [変動]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,800 [変動]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,000 [変動]</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,700 [変動]</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -10377,7 +11081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12503,6 +13207,158 @@
         </is>
       </c>
       <c r="AD14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -12519,7 +13375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13245,6 +14101,58 @@
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -13261,7 +14169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14687,6 +15595,108 @@
         </is>
       </c>
       <c r="T14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -14703,7 +15713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16269,6 +17279,118 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>4,300</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1953,6 +1953,108 @@
       <c r="T15" t="inlineStr">
         <is>
           <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
         </is>
       </c>
     </row>
@@ -1967,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3570,6 +3672,113 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -3586,7 +3795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4664,6 +4873,78 @@
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -4680,7 +4961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6208,6 +6489,108 @@
         </is>
       </c>
       <c r="T15" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15,700 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9,100 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -6224,7 +6607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7452,6 +7835,88 @@
         </is>
       </c>
       <c r="P15" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -7468,7 +7933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9671,6 +10136,153 @@
         </is>
       </c>
       <c r="AC15" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -9687,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11065,6 +11677,98 @@
         </is>
       </c>
       <c r="R15" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5,800 [変動]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,800 [変動]</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -11081,7 +11785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13359,6 +14063,158 @@
         </is>
       </c>
       <c r="AD15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -13375,7 +14231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14153,6 +15009,58 @@
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -14169,7 +15077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15697,6 +16605,108 @@
         </is>
       </c>
       <c r="T15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -15713,7 +16723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17391,6 +18401,118 @@
         </is>
       </c>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>4,300</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,6 +2053,108 @@
         </is>
       </c>
       <c r="T16" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,300 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>5,200 完売</t>
         </is>
@@ -2069,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3779,6 +3881,113 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22,100</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11,300</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -3795,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4945,6 +5154,78 @@
         </is>
       </c>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -4961,7 +5242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6591,6 +6872,108 @@
         </is>
       </c>
       <c r="T16" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -6607,7 +6990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7917,6 +8300,88 @@
         </is>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -7933,7 +8398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8082,6 +8547,11 @@
           <t>バリュープライスシートBホーム</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートＣホーム</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8229,6 +8699,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8376,6 +8847,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8523,6 +8995,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8670,6 +9143,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8817,6 +9291,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8964,6 +9439,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9111,6 +9587,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9258,6 +9735,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9405,6 +9883,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9552,6 +10031,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9699,6 +10179,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9846,6 +10327,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9993,6 +10475,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10140,6 +10623,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10285,6 +10769,159 @@
       <c r="AC16" t="inlineStr">
         <is>
           <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12,800 完売</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11769,6 +12406,98 @@
         </is>
       </c>
       <c r="R16" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5,800 [変動]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,400 [変動]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,800 [変動]</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -11785,7 +12514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14215,6 +14944,158 @@
         </is>
       </c>
       <c r="AD16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -14231,7 +15112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15061,6 +15942,58 @@
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -15077,7 +16010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16707,6 +17640,108 @@
         </is>
       </c>
       <c r="T16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -16723,7 +17758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18515,6 +19550,118 @@
       <c r="V16" t="inlineStr">
         <is>
           <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>4,200</t>
         </is>
       </c>
     </row>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3988,6 +3988,113 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22,500</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4004,7 +4111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5226,6 +5333,78 @@
         </is>
       </c>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -5242,7 +5421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6974,6 +7153,108 @@
         </is>
       </c>
       <c r="T17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -6990,7 +7271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8382,6 +8663,88 @@
         </is>
       </c>
       <c r="P17" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
@@ -8398,7 +8761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10920,6 +11283,158 @@
         </is>
       </c>
       <c r="AD17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12,800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -10936,7 +11451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12498,6 +13013,98 @@
         </is>
       </c>
       <c r="R17" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5,900 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>5,000 [変動]</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -12514,7 +13121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15096,6 +15703,158 @@
         </is>
       </c>
       <c r="AD17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -15112,7 +15871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15994,6 +16753,58 @@
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -16010,7 +16821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17742,6 +18553,108 @@
         </is>
       </c>
       <c r="T17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -17758,7 +18671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19660,6 +20573,118 @@
         </is>
       </c>
       <c r="V17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4095,6 +4095,113 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22,400</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,950</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6,950</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6,450</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,450</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4111,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5405,6 +5512,78 @@
         </is>
       </c>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -11451,7 +11630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13105,6 +13284,98 @@
         </is>
       </c>
       <c r="R18" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5,900 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>5,000 [変動]</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -13121,7 +13392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15855,6 +16126,158 @@
         </is>
       </c>
       <c r="AD18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -15871,7 +16294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16805,6 +17228,58 @@
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -16821,7 +17296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18655,6 +19130,108 @@
         </is>
       </c>
       <c r="T18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -18671,7 +19248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20685,6 +21262,118 @@
         </is>
       </c>
       <c r="V18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4202,6 +4202,113 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22,600</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4218,7 +4325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5584,6 +5691,78 @@
         </is>
       </c>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -11630,7 +11809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13376,6 +13555,98 @@
         </is>
       </c>
       <c r="R19" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5,900 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>5,000 [変動]</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -13392,7 +13663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16278,6 +16549,158 @@
         </is>
       </c>
       <c r="AD19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -16294,7 +16717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17280,6 +17703,58 @@
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -17296,7 +17771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19232,6 +19707,108 @@
         </is>
       </c>
       <c r="T19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -19248,7 +19825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21374,6 +21951,118 @@
         </is>
       </c>
       <c r="V19" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4309,6 +4309,113 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>22,600</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4325,7 +4432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5763,6 +5870,78 @@
         </is>
       </c>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -11809,7 +11988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13647,6 +13826,98 @@
         </is>
       </c>
       <c r="R20" t="inlineStr">
+        <is>
+          <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10,000 [変動]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,200 [変動]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5,900 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5,200 [変動]</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>5,000 [変動]</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
         </is>
@@ -13663,7 +13934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16701,6 +16972,158 @@
         </is>
       </c>
       <c r="AD20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -16717,7 +17140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17755,6 +18178,58 @@
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -17771,7 +18246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19809,6 +20284,108 @@
         </is>
       </c>
       <c r="T20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -19825,7 +20402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22063,6 +22640,118 @@
         </is>
       </c>
       <c r="V20" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4416,6 +4416,113 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22,600</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4432,7 +4539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5942,6 +6049,78 @@
         </is>
       </c>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -11988,7 +12167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13920,6 +14099,98 @@
       <c r="R21" t="inlineStr">
         <is>
           <t>14,000 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8,600 [変動]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5,300 [変動]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5,900 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>4,000 [変動]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
         </is>
       </c>
     </row>
@@ -13934,7 +14205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17124,6 +17395,158 @@
         </is>
       </c>
       <c r="AD21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -17140,7 +17563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18230,6 +18653,58 @@
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -18246,7 +18721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20386,6 +20861,108 @@
         </is>
       </c>
       <c r="T21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -20402,7 +20979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22752,6 +23329,118 @@
         </is>
       </c>
       <c r="V21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4523,6 +4523,113 @@
         </is>
       </c>
       <c r="U22" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11,700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4539,7 +4646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6121,6 +6228,78 @@
         </is>
       </c>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -12167,7 +12346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14189,6 +14368,98 @@
         </is>
       </c>
       <c r="R22" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8,900 [変動]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6,100 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -14205,7 +14476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17547,6 +17818,158 @@
         </is>
       </c>
       <c r="AD22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -17563,7 +17986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18705,6 +19128,58 @@
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -18721,7 +19196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20963,6 +21438,108 @@
         </is>
       </c>
       <c r="T22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -20979,7 +21556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23441,6 +24018,118 @@
         </is>
       </c>
       <c r="V22" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-12 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4630,6 +4630,113 @@
         </is>
       </c>
       <c r="U23" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22,400</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4646,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6300,6 +6407,78 @@
         </is>
       </c>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -12346,7 +12525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14460,6 +14639,98 @@
         </is>
       </c>
       <c r="R23" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6,100 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4,100 [変動]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -14476,7 +14747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17970,6 +18241,158 @@
         </is>
       </c>
       <c r="AD23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -17986,7 +18409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19180,6 +19603,58 @@
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19196,7 +19671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21540,6 +22015,108 @@
         </is>
       </c>
       <c r="T23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -21556,7 +22133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24130,6 +24707,118 @@
         </is>
       </c>
       <c r="V23" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4737,6 +4737,113 @@
         </is>
       </c>
       <c r="U24" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>22,600</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4753,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6479,6 +6586,78 @@
         </is>
       </c>
       <c r="N24" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -12525,7 +12704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14731,6 +14910,98 @@
         </is>
       </c>
       <c r="R24" t="inlineStr">
+        <is>
+          <t>14,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8,800 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6,300 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>4,300 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>14,600 [変動]</t>
         </is>
@@ -14747,7 +15018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18393,6 +18664,158 @@
         </is>
       </c>
       <c r="AD24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -18409,7 +18832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19655,6 +20078,58 @@
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19671,7 +20146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22117,6 +22592,108 @@
         </is>
       </c>
       <c r="T24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -22133,7 +22710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24819,6 +25396,118 @@
         </is>
       </c>
       <c r="V24" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4844,6 +4844,113 @@
         </is>
       </c>
       <c r="U25" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4860,7 +4967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6658,6 +6765,78 @@
         </is>
       </c>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -15018,7 +15197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18816,6 +18995,158 @@
         </is>
       </c>
       <c r="AD25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -18832,7 +19163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18843,45 +19174,55 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>セブン-イレブンピッチサイドシ-ト</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>バック指定席（ホーム）</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ビジター指定席</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ホーム応援エリア席</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>メインミックス指定席</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ＦＡＧＩシート　（指定席）</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ｓ指定席　北</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Ｓ指定席　南</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ＳＡ指定席</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ＳＢ指定席</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ＳＳ指定席</t>
         </is>
@@ -18893,47 +19234,49 @@
           <t>2026-07-26 11:07</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -18945,47 +19288,49 @@
           <t>2026-07-26 16:14</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -18997,47 +19342,49 @@
           <t>2026-07-26 20:35</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19049,47 +19396,49 @@
           <t>2026-07-27 00:02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19101,47 +19450,49 @@
           <t>2026-07-27 19:52</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19153,47 +19504,49 @@
           <t>2026-07-28 00:51</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19205,47 +19558,49 @@
           <t>2026-07-28 06:01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19257,47 +19612,49 @@
           <t>2026-07-28 09:14</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19309,47 +19666,49 @@
           <t>2026-07-29 06:01</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19361,47 +19720,49 @@
           <t>2026-07-30 06:01</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19413,47 +19774,49 @@
           <t>2026-08-01 06:01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19465,47 +19828,49 @@
           <t>2026-08-02 06:03</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19517,47 +19882,49 @@
           <t>2026-08-03 06:01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19569,47 +19936,49 @@
           <t>2026-08-04 06:01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19621,47 +19990,49 @@
           <t>2026-08-05 06:03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19673,47 +20044,49 @@
           <t>2026-08-06 06:01</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19725,47 +20098,49 @@
           <t>2026-08-08 06:01</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19777,47 +20152,49 @@
           <t>2026-08-09 06:01</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19829,47 +20206,49 @@
           <t>2026-08-09 14:32</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19881,47 +20260,49 @@
           <t>2026-08-10 06:01</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19933,47 +20314,49 @@
           <t>2026-08-11 06:01</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -19985,47 +20368,49 @@
           <t>2026-08-12 06:01</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -20037,47 +20422,49 @@
           <t>2026-08-13 06:01</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
@@ -20089,49 +20476,113 @@
           <t>2026-08-14 06:01</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>5,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5,700</t>
         </is>
       </c>
     </row>
@@ -20146,7 +20597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22694,6 +23145,108 @@
         </is>
       </c>
       <c r="T25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -22710,7 +23263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25508,6 +26061,118 @@
         </is>
       </c>
       <c r="V25" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4951,6 +4951,113 @@
         </is>
       </c>
       <c r="U26" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -4967,7 +5074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6837,6 +6944,78 @@
         </is>
       </c>
       <c r="N26" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -20597,7 +20776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23247,6 +23426,108 @@
         </is>
       </c>
       <c r="T26" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -23263,7 +23544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26173,6 +26454,118 @@
         </is>
       </c>
       <c r="V26" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5058,113 @@
         </is>
       </c>
       <c r="U27" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-17 06:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -5074,7 +5181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7016,6 +7123,78 @@
         </is>
       </c>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-17 06:01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -20776,7 +20955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23528,6 +23707,108 @@
         </is>
       </c>
       <c r="T27" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-17 06:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -23544,7 +23825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26566,6 +26847,118 @@
         </is>
       </c>
       <c r="V27" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-17 06:01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5165,6 +5165,113 @@
         </is>
       </c>
       <c r="U28" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18 06:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>22,000 完売</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -5181,7 +5288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7195,6 +7302,78 @@
         </is>
       </c>
       <c r="N28" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18 06:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -20955,7 +21134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23809,6 +23988,108 @@
         </is>
       </c>
       <c r="T28" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18 06:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -23825,7 +24106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26959,6 +27240,118 @@
         </is>
       </c>
       <c r="V28" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18 06:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5272,6 +5272,113 @@
         </is>
       </c>
       <c r="U29" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-19 06:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>22,000 完売</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -5288,7 +5395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7374,6 +7481,78 @@
         </is>
       </c>
       <c r="N29" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-19 06:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -21134,7 +21313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24090,6 +24269,108 @@
         </is>
       </c>
       <c r="T29" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-19 06:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -24106,7 +24387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27352,6 +27633,118 @@
         </is>
       </c>
       <c r="V29" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-19 06:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5379,6 +5379,113 @@
         </is>
       </c>
       <c r="U30" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-21 06:01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>22,000 完売</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -5395,7 +5502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7553,6 +7660,78 @@
         </is>
       </c>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-21 06:01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -21313,7 +21492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24373,6 +24552,108 @@
       <c r="T30" t="inlineStr">
         <is>
           <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-21 06:01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>4,500</t>
         </is>
       </c>
     </row>
@@ -24387,7 +24668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27745,6 +28026,118 @@
         </is>
       </c>
       <c r="V30" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-21 06:01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5486,6 +5486,113 @@
         </is>
       </c>
       <c r="U31" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-22 06:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>22,000 完売</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -5502,7 +5609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7732,6 +7839,78 @@
         </is>
       </c>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-22 06:01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -24668,7 +24847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28138,6 +28317,118 @@
         </is>
       </c>
       <c r="V31" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-22 06:01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -2171,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5593,6 +5593,113 @@
         </is>
       </c>
       <c r="U32" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-23 14:19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>22,000 完売</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
         <is>
           <t>7,700</t>
         </is>
@@ -5609,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7911,6 +8018,78 @@
         </is>
       </c>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-23 14:19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8090,6 +8090,78 @@
         </is>
       </c>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-24 06:01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8162,6 +8162,78 @@
         </is>
       </c>
       <c r="N34" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-25 06:01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8234,6 +8234,78 @@
         </is>
       </c>
       <c r="N35" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-26 06:01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8306,6 +8306,78 @@
         </is>
       </c>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-27 06:01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8378,6 +8378,78 @@
         </is>
       </c>
       <c r="N37" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-28 06:01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8452,6 +8452,78 @@
       <c r="N38" t="inlineStr">
         <is>
           <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3,100 完売</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>3,400</t>
         </is>
       </c>
     </row>
